--- a/data/point_csv/point_sample_dnp3.xlsx
+++ b/data/point_csv/point_sample_dnp3.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="遥测" sheetId="1" r:id="R4c6725d6215d463a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="遥信" sheetId="2" r:id="R44879ec63d584f8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="遥控" sheetId="3" r:id="Rda2f7adc2b2a4f0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="遥调" sheetId="4" r:id="R7e37d8b1170a4d71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="遥测" sheetId="1" r:id="Rff728da9c64c4ec6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="遥信" sheetId="2" r:id="Rcf475797cfb24a68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="遥控" sheetId="3" r:id="R6b6c4bbeb4464ebc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="遥调" sheetId="4" r:id="R1363f040685346a7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -239,6 +239,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="6" max="6" width="19" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
@@ -313,7 +316,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2" t="str">
-        <x:v>0x41</x:v>
+        <x:v>INT32_ABCD</x:v>
       </x:c>
       <x:c r="G2" t="n">
         <x:v>0.1</x:v>
@@ -369,7 +372,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3" t="str">
-        <x:v>0x41</x:v>
+        <x:v>INT32_ABCD</x:v>
       </x:c>
       <x:c r="G3" t="n">
         <x:v>0.1</x:v>
@@ -425,7 +428,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>0x41</x:v>
+        <x:v>INT32_ABCD</x:v>
       </x:c>
       <x:c r="G4" t="n">
         <x:v>0.1</x:v>
@@ -481,7 +484,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" t="str">
-        <x:v>0x41</x:v>
+        <x:v>INT32_ABCD</x:v>
       </x:c>
       <x:c r="G5" t="n">
         <x:v>0.1</x:v>
@@ -537,7 +540,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F6" t="str">
-        <x:v>0x41</x:v>
+        <x:v>INT32_ABCD</x:v>
       </x:c>
       <x:c r="G6" t="n">
         <x:v>0.1</x:v>
@@ -593,7 +596,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F7" t="str">
-        <x:v>0x41</x:v>
+        <x:v>INT32_ABCD</x:v>
       </x:c>
       <x:c r="G7" t="n">
         <x:v>0.1</x:v>
@@ -649,7 +652,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F8" t="str">
-        <x:v>0x41</x:v>
+        <x:v>INT32_ABCD</x:v>
       </x:c>
       <x:c r="G8" t="n">
         <x:v>0.01</x:v>
@@ -705,7 +708,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F9" t="str">
-        <x:v>0x41</x:v>
+        <x:v>INT32_ABCD</x:v>
       </x:c>
       <x:c r="G9" t="n">
         <x:v>0.1</x:v>
@@ -761,7 +764,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F10" t="str">
-        <x:v>0x41</x:v>
+        <x:v>INT32_ABCD</x:v>
       </x:c>
       <x:c r="G10" t="n">
         <x:v>0.1</x:v>
@@ -817,7 +820,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F11" t="str">
-        <x:v>0x41</x:v>
+        <x:v>INT32_ABCD</x:v>
       </x:c>
       <x:c r="G11" t="n">
         <x:v>0.01</x:v>
@@ -864,6 +867,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="6" max="6" width="19" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
@@ -929,7 +935,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F2" t="str">
-        <x:v>0x20</x:v>
+        <x:v>UINT16_AB</x:v>
       </x:c>
       <x:c r="G2" t="n">
         <x:v>0</x:v>
@@ -976,7 +982,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F3" t="str">
-        <x:v>0x20</x:v>
+        <x:v>UINT16_AB</x:v>
       </x:c>
       <x:c r="G3" t="n">
         <x:v>0</x:v>
@@ -1023,7 +1029,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>0x20</x:v>
+        <x:v>UINT16_AB</x:v>
       </x:c>
       <x:c r="G4" t="n">
         <x:v>0</x:v>
@@ -1070,7 +1076,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F5" t="str">
-        <x:v>0x20</x:v>
+        <x:v>UINT16_AB</x:v>
       </x:c>
       <x:c r="G5" t="n">
         <x:v>0</x:v>
@@ -1117,7 +1123,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F6" t="str">
-        <x:v>0x20</x:v>
+        <x:v>UINT16_AB</x:v>
       </x:c>
       <x:c r="G6" t="n">
         <x:v>0</x:v>
@@ -1164,7 +1170,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F7" t="str">
-        <x:v>0x20</x:v>
+        <x:v>UINT16_AB</x:v>
       </x:c>
       <x:c r="G7" t="n">
         <x:v>0</x:v>
@@ -1202,6 +1208,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="6" max="6" width="19" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
@@ -1285,7 +1294,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F2" t="str">
-        <x:v>0x20</x:v>
+        <x:v>UINT16_AB</x:v>
       </x:c>
       <x:c r="G2" t="n">
         <x:v>0</x:v>
@@ -1350,7 +1359,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F3" t="str">
-        <x:v>0x20</x:v>
+        <x:v>UINT16_AB</x:v>
       </x:c>
       <x:c r="G3" t="n">
         <x:v>0</x:v>
@@ -1415,7 +1424,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>0x20</x:v>
+        <x:v>UINT16_AB</x:v>
       </x:c>
       <x:c r="G4" t="n">
         <x:v>0</x:v>
@@ -1480,7 +1489,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F5" t="str">
-        <x:v>0x20</x:v>
+        <x:v>UINT16_AB</x:v>
       </x:c>
       <x:c r="G5" t="n">
         <x:v>0</x:v>
@@ -1545,7 +1554,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F6" t="str">
-        <x:v>0x20</x:v>
+        <x:v>UINT16_AB</x:v>
       </x:c>
       <x:c r="G6" t="n">
         <x:v>0</x:v>
@@ -1601,6 +1610,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="6" max="6" width="19" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
@@ -1678,7 +1690,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="F2" t="str">
-        <x:v>0x41</x:v>
+        <x:v>INT32_ABCD</x:v>
       </x:c>
       <x:c r="G2" t="n">
         <x:v>0.1</x:v>
@@ -1737,7 +1749,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="F3" t="str">
-        <x:v>0x41</x:v>
+        <x:v>INT32_ABCD</x:v>
       </x:c>
       <x:c r="G3" t="n">
         <x:v>0.1</x:v>
@@ -1796,7 +1808,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>0x41</x:v>
+        <x:v>INT32_ABCD</x:v>
       </x:c>
       <x:c r="G4" t="n">
         <x:v>0.1</x:v>
